--- a/artfynd/A 1110-2026 artfynd.xlsx
+++ b/artfynd/A 1110-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>392358</v>
+        <v>87858987</v>
       </c>
       <c r="B2" t="n">
-        <v>89402</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Vad, ca 2 km söderut, Upl</t>
+          <t>Mårdfallsbottnen 3,5 km S om Västlands kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643807.4373401727</v>
+        <v>643965</v>
       </c>
       <c r="R2" t="n">
-        <v>6700498.116843231</v>
+        <v>6700527</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-08-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar på ca 40 cm grov asp</t>
+          <t>2020-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,42 +766,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Uppföljning av skyddade områden</t>
-        </is>
-      </c>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66022335</v>
+        <v>392358</v>
       </c>
       <c r="B3" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,34 +811,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kraftledningsgata, Upl</t>
+          <t>Östra Vad, ca 2 km söderut, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>643868.178329019</v>
+        <v>643807</v>
       </c>
       <c r="R3" t="n">
-        <v>6700490.14267335</v>
+        <v>6700498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +874,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar på ca 40 cm grov asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,31 +895,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emelie Grabbe</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Emelie Grabbe</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66022334</v>
+        <v>75631851</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,37 +931,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kraftledningsgata, Upl</t>
+          <t>Järmossen 3 km SSO om Västlands kyrka, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>643927.8941396701</v>
+        <v>643811</v>
       </c>
       <c r="R4" t="n">
-        <v>6700383.232569941</v>
+        <v>6700538</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +994,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-10-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 ex. på levande asp, omkr. 119 cm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,31 +1015,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Levande asp. # Asp</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emelie Grabbe</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Emelie Grabbe</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66022336</v>
+        <v>87858996</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,34 +1052,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kraftledningsgata, Upl</t>
+          <t>Mårdfallsbottnen 3,5 km S om Västlands kyrka, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>643856.9513858955</v>
+        <v>643965</v>
       </c>
       <c r="R5" t="n">
-        <v>6700510.959451732</v>
+        <v>6700527</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,22 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,18 +1128,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emelie Grabbe</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Emelie Grabbe</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1149,16 +1155,11 @@
         <v>66021941</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>643911.8781333823</v>
+        <v>643912</v>
       </c>
       <c r="R6" t="n">
-        <v>6700399.903867562</v>
+        <v>6700400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,19 +1220,9 @@
           <t>2017-04-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66022337</v>
+        <v>66022336</v>
       </c>
       <c r="B7" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>643907.0943461416</v>
+        <v>643857</v>
       </c>
       <c r="R7" t="n">
-        <v>6700408.120235297</v>
+        <v>6700511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1317,9 @@
           <t>2017-04-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-04-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,15 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75631851</v>
+        <v>66022335</v>
       </c>
       <c r="B8" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,46 +1357,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Järmossen 3 km SSO om Västlands kyrka, Upl</t>
+          <t>Kraftledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>643810.796210693</v>
+        <v>643868</v>
       </c>
       <c r="R8" t="n">
-        <v>6700538.301977844</v>
+        <v>6700490</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,27 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1999-10-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1999-10-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 ex. på levande asp, omkr. 119 cm.</t>
+          <t>2017-04-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,29 +1427,213 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Levande asp. # Asp</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Emelie Grabbe</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Via Emelie Grabbe</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>66022337</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>643907</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6700408</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-04-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-04-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emelie Grabbe</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Emelie Grabbe</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>66022334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>643928</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6700383</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-04-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-04-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emelie Grabbe</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Emelie Grabbe</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1110-2026 artfynd.xlsx
+++ b/artfynd/A 1110-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87858987</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/392358</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75631851</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87858996</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66021941</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66022336</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66022335</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66022337</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,8 +1679,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66022334</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>